--- a/Supplementary Files/Supplementary_File_SF4.xlsx
+++ b/Supplementary Files/Supplementary_File_SF4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -76,9 +76,6 @@
     <t>We are taking best compressor setting of the general purpose compressor w.r.t. C.Size (C.Size - Compressed Size).</t>
   </si>
   <si>
-    <t>NF</t>
-  </si>
-  <si>
     <t>S-GZip</t>
   </si>
   <si>
@@ -127,7 +124,7 @@
     <t>The best result is marked by bold.</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 5: The mean time (s) and standard deviation of three runs required by the S-Gzip, S-BZip2, NF, CoGI, NAF, P-Gzip, P-BZip2, and HGC encoders on a DNA corpus that has fifteen benchmark sequences, arranged according to file size.          
+    <t xml:space="preserve">Table 5: The mean time (s) and standard deviation of three runs required by the S-Gzip, S-BZip2, CoGI, NAF, P-Gzip, P-BZip2, and HGC encoders on a DNA corpus that has fifteen benchmark sequences, arranged according to file size.          
 </t>
   </si>
 </sst>
@@ -686,7 +683,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -715,9 +712,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -740,9 +734,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1155,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -1163,104 +1154,94 @@
     <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.7109375" customWidth="1"/>
-    <col min="6" max="11" width="6.7109375" style="6" customWidth="1"/>
-    <col min="12" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" style="6" customWidth="1"/>
+    <col min="10" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="32.25" customHeight="1">
-      <c r="A1" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-    </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" ht="15.75" thickBot="1">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="48" customHeight="1">
+      <c r="A1" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+    </row>
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="15.75" thickBot="1">
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" thickBot="1">
-      <c r="A3" s="42" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="16.5" thickBot="1">
+      <c r="A3" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="42" t="s">
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+    </row>
+    <row r="4" spans="1:15" ht="16.5" thickBot="1">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="44" t="s">
+      <c r="C4" s="41"/>
+      <c r="D4" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" thickBot="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43" t="s">
+      <c r="K4" s="41"/>
+      <c r="L4" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="43"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.75">
+      <c r="O4" s="41"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1270,50 +1251,44 @@
       <c r="C5" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="F5" s="23">
-        <v>1.012</v>
-      </c>
-      <c r="G5" s="23">
-        <v>1E-3</v>
+      <c r="F5" s="27">
+        <v>0.155</v>
+      </c>
+      <c r="G5" s="28">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H5" s="29">
-        <v>0.155</v>
-      </c>
-      <c r="I5" s="30">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J5" s="31">
         <v>1.08</v>
       </c>
-      <c r="K5" s="31">
+      <c r="I5" s="29">
         <v>4.3999999999999997E-2</v>
       </c>
+      <c r="J5" s="20">
+        <v>2E-3</v>
+      </c>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
       <c r="L5" s="22">
-        <v>2E-3</v>
-      </c>
-      <c r="M5" s="15">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M5" s="3">
         <v>0</v>
       </c>
-      <c r="N5" s="24">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
-      <c r="P5" s="33">
+      <c r="N5" s="31">
         <v>3.5139999999999998</v>
       </c>
-      <c r="Q5" s="32">
+      <c r="O5" s="30">
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75">
+    <row r="6" spans="1:15" ht="15.75">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1323,50 +1298,44 @@
       <c r="C6" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6" s="21">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="G6" s="12">
-        <v>1E-3</v>
+      <c r="F6" s="27">
+        <v>0.16</v>
+      </c>
+      <c r="G6" s="28">
+        <v>2E-3</v>
       </c>
       <c r="H6" s="29">
-        <v>0.16</v>
-      </c>
-      <c r="I6" s="30">
-        <v>2E-3</v>
-      </c>
-      <c r="J6" s="31">
         <v>1.1399999999999999</v>
       </c>
-      <c r="K6" s="31">
+      <c r="I6" s="29">
         <v>0.15</v>
       </c>
-      <c r="L6" s="22">
+      <c r="J6" s="20">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="M6" s="15">
+      <c r="K6" s="14">
         <v>0</v>
       </c>
-      <c r="N6" s="23">
+      <c r="L6" s="21">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="O6" s="4">
+      <c r="M6" s="4">
         <v>0</v>
       </c>
-      <c r="P6" s="33">
+      <c r="N6" s="31">
         <v>3.819</v>
       </c>
-      <c r="Q6" s="32">
+      <c r="O6" s="30">
         <v>0.24099999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75">
+    <row r="7" spans="1:15" ht="15.75">
       <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1376,50 +1345,44 @@
       <c r="C7" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="F7" s="21">
-        <v>1.012</v>
-      </c>
-      <c r="G7" s="12">
-        <v>1E-3</v>
+      <c r="F7" s="27">
+        <v>0.186</v>
+      </c>
+      <c r="G7" s="28">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H7" s="29">
-        <v>0.186</v>
-      </c>
-      <c r="I7" s="30">
+        <v>1.026</v>
+      </c>
+      <c r="I7" s="29">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J7" s="20">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J7" s="31">
-        <v>1.026</v>
-      </c>
-      <c r="K7" s="31">
+      <c r="K7" s="14">
+        <v>0</v>
+      </c>
+      <c r="L7" s="21">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="L7" s="22">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="M7" s="15">
+      <c r="M7" s="4">
         <v>0</v>
       </c>
-      <c r="N7" s="23">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="33">
+      <c r="N7" s="31">
         <v>4.165</v>
       </c>
-      <c r="Q7" s="32">
+      <c r="O7" s="30">
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75">
+    <row r="8" spans="1:15" ht="15.75">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1429,50 +1392,44 @@
       <c r="C8" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>0.155</v>
       </c>
       <c r="E8" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F8" s="21">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="G8" s="12">
-        <v>1E-3</v>
+      <c r="F8" s="27">
+        <v>0.316</v>
+      </c>
+      <c r="G8" s="28">
+        <v>2E-3</v>
       </c>
       <c r="H8" s="29">
-        <v>0.316</v>
-      </c>
-      <c r="I8" s="30">
-        <v>2E-3</v>
-      </c>
-      <c r="J8" s="31">
         <v>1.0349999999999999</v>
       </c>
-      <c r="K8" s="31">
+      <c r="I8" s="29">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L8" s="22">
+      <c r="J8" s="20">
         <v>2.3E-2</v>
       </c>
-      <c r="M8" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N8" s="23">
+      <c r="K8" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="L8" s="21">
         <v>4.7E-2</v>
       </c>
-      <c r="O8" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="P8" s="33">
+      <c r="M8" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="N8" s="31">
         <v>4.7530000000000001</v>
       </c>
-      <c r="Q8" s="32">
+      <c r="O8" s="30">
         <v>0.39300000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75">
+    <row r="9" spans="1:15" ht="15.75">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1482,50 +1439,44 @@
       <c r="C9" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>0.16300000000000001</v>
       </c>
       <c r="E9" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F9" s="21">
-        <v>1.012</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="F9" s="27">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="G9" s="28">
         <v>1E-3</v>
       </c>
       <c r="H9" s="29">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="I9" s="30">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="31">
         <v>1.032</v>
       </c>
-      <c r="K9" s="31">
+      <c r="I9" s="29">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="L9" s="22">
+      <c r="J9" s="20">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="M9" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N9" s="23">
+      <c r="K9" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="L9" s="21">
         <v>4.7E-2</v>
       </c>
-      <c r="O9" s="4">
+      <c r="M9" s="4">
         <v>0</v>
       </c>
-      <c r="P9" s="33">
+      <c r="N9" s="31">
         <v>4.3730000000000002</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="O9" s="30">
         <v>0.308</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75">
+    <row r="10" spans="1:15" ht="15.75">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1535,50 +1486,44 @@
       <c r="C10" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>0.378</v>
       </c>
       <c r="E10" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F10" s="21">
-        <v>1.012</v>
-      </c>
-      <c r="G10" s="12">
-        <v>1E-3</v>
+      <c r="F10" s="27">
+        <v>0.621</v>
+      </c>
+      <c r="G10" s="28">
+        <v>2E-3</v>
       </c>
       <c r="H10" s="29">
-        <v>0.621</v>
-      </c>
-      <c r="I10" s="30">
+        <v>1.042</v>
+      </c>
+      <c r="I10" s="29">
         <v>2E-3</v>
       </c>
-      <c r="J10" s="31">
-        <v>1.042</v>
-      </c>
-      <c r="K10" s="31">
-        <v>2E-3</v>
-      </c>
-      <c r="L10" s="22">
+      <c r="J10" s="20">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="M10" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N10" s="23">
+      <c r="K10" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="L10" s="21">
         <v>0.115</v>
       </c>
-      <c r="O10" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="P10" s="33">
+      <c r="M10" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="N10" s="31">
         <v>5.5979999999999999</v>
       </c>
-      <c r="Q10" s="32">
+      <c r="O10" s="30">
         <v>0.30399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75">
+    <row r="11" spans="1:15" ht="15.75">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1588,50 +1533,44 @@
       <c r="C11" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>0.443</v>
       </c>
       <c r="E11" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F11" s="21">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="G11" s="12">
+      <c r="F11" s="27">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="G11" s="28">
         <v>1E-3</v>
       </c>
       <c r="H11" s="29">
-        <v>0.71699999999999997</v>
-      </c>
-      <c r="I11" s="30">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="31">
         <v>1.0449999999999999</v>
       </c>
-      <c r="K11" s="31">
+      <c r="I11" s="29">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L11" s="22">
+      <c r="J11" s="20">
         <v>6.3E-2</v>
       </c>
-      <c r="M11" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N11" s="23">
+      <c r="K11" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="L11" s="21">
         <v>0.13800000000000001</v>
       </c>
-      <c r="O11" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="P11" s="33">
+      <c r="M11" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="N11" s="31">
         <v>6.0010000000000003</v>
       </c>
-      <c r="Q11" s="32">
+      <c r="O11" s="30">
         <v>0.51800000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75">
+    <row r="12" spans="1:15" ht="15.75">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
@@ -1641,50 +1580,44 @@
       <c r="C12" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="19">
         <v>0.85799999999999998</v>
       </c>
       <c r="E12" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F12" s="21">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="G12" s="12">
-        <v>1E-3</v>
+      <c r="F12" s="27">
+        <v>1.3720000000000001</v>
+      </c>
+      <c r="G12" s="28">
+        <v>2E-3</v>
       </c>
       <c r="H12" s="29">
-        <v>1.3720000000000001</v>
-      </c>
-      <c r="I12" s="30">
-        <v>2E-3</v>
-      </c>
-      <c r="J12" s="31">
         <v>1.0609999999999999</v>
       </c>
-      <c r="K12" s="31">
+      <c r="I12" s="29">
         <v>4.0000000000000001E-3</v>
       </c>
+      <c r="J12" s="20">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="K12" s="14">
+        <v>1E-3</v>
+      </c>
       <c r="L12" s="22">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="M12" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N12" s="24">
         <v>0.246</v>
       </c>
-      <c r="O12" s="3">
+      <c r="M12" s="3">
         <v>0</v>
       </c>
-      <c r="P12" s="33">
+      <c r="N12" s="31">
         <v>6.6779999999999999</v>
       </c>
-      <c r="Q12" s="32">
+      <c r="O12" s="30">
         <v>0.28499999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75">
+    <row r="13" spans="1:15" ht="15.75">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -1694,50 +1627,44 @@
       <c r="C13" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <v>0.86699999999999999</v>
       </c>
       <c r="E13" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F13" s="21">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="G13" s="12">
-        <v>1E-3</v>
+      <c r="F13" s="27">
+        <v>1.88</v>
+      </c>
+      <c r="G13" s="28">
+        <v>0.01</v>
       </c>
       <c r="H13" s="29">
-        <v>1.88</v>
-      </c>
-      <c r="I13" s="30">
-        <v>0.01</v>
-      </c>
-      <c r="J13" s="31">
         <v>1.071</v>
       </c>
-      <c r="K13" s="31">
+      <c r="I13" s="29">
         <v>2E-3</v>
       </c>
+      <c r="J13" s="20">
+        <v>0.121</v>
+      </c>
+      <c r="K13" s="14">
+        <v>1E-3</v>
+      </c>
       <c r="L13" s="22">
-        <v>0.121</v>
-      </c>
-      <c r="M13" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N13" s="24">
         <v>0.26900000000000002</v>
       </c>
-      <c r="O13" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="P13" s="33">
+      <c r="M13" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="N13" s="31">
         <v>7.157</v>
       </c>
-      <c r="Q13" s="32">
+      <c r="O13" s="30">
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75">
+    <row r="14" spans="1:15" ht="15.75">
       <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
@@ -1747,50 +1674,44 @@
       <c r="C14" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <v>1.0089999999999999</v>
       </c>
       <c r="E14" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F14" s="21">
-        <v>1.014</v>
-      </c>
-      <c r="G14" s="12">
-        <v>1E-3</v>
+      <c r="F14" s="27">
+        <v>3.82</v>
+      </c>
+      <c r="G14" s="28">
+        <v>0.01</v>
       </c>
       <c r="H14" s="29">
-        <v>3.82</v>
-      </c>
-      <c r="I14" s="30">
-        <v>0.01</v>
-      </c>
-      <c r="J14" s="31">
         <v>1.073</v>
       </c>
-      <c r="K14" s="31">
+      <c r="I14" s="29">
         <v>6.0000000000000001E-3</v>
       </c>
+      <c r="J14" s="20">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="K14" s="14">
+        <v>1E-3</v>
+      </c>
       <c r="L14" s="22">
-        <v>0.14399999999999999</v>
-      </c>
-      <c r="M14" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N14" s="24">
         <v>0.32100000000000001</v>
       </c>
-      <c r="O14" s="3">
+      <c r="M14" s="3">
         <v>2E-3</v>
       </c>
-      <c r="P14" s="33">
+      <c r="N14" s="31">
         <v>7.4089999999999998</v>
       </c>
-      <c r="Q14" s="32">
+      <c r="O14" s="30">
         <v>0.186</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75">
+    <row r="15" spans="1:15" ht="15.75">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1800,50 +1721,44 @@
       <c r="C15" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <v>2.4489999999999998</v>
       </c>
       <c r="E15" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F15" s="21">
-        <v>1.0149999999999999</v>
-      </c>
-      <c r="G15" s="12">
-        <v>1E-3</v>
+      <c r="F15" s="27">
+        <v>4.3929999999999998</v>
+      </c>
+      <c r="G15" s="28">
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H15" s="29">
-        <v>4.3929999999999998</v>
-      </c>
-      <c r="I15" s="30">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="J15" s="31">
         <v>1.228</v>
       </c>
-      <c r="K15" s="31">
+      <c r="I15" s="29">
         <v>3.0000000000000001E-3</v>
       </c>
+      <c r="J15" s="20">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="K15" s="14">
+        <v>1E-3</v>
+      </c>
       <c r="L15" s="22">
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="M15" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="N15" s="24">
         <v>0.75800000000000001</v>
       </c>
-      <c r="O15" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="P15" s="33">
+      <c r="M15" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="N15" s="31">
         <v>12.815</v>
       </c>
-      <c r="Q15" s="32">
+      <c r="O15" s="30">
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75">
+    <row r="16" spans="1:15" ht="15.75">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -1853,50 +1768,44 @@
       <c r="C16" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="19">
         <v>4.1929999999999996</v>
       </c>
       <c r="E16" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F16" s="21">
-        <v>1.1850000000000001</v>
-      </c>
-      <c r="G16" s="12">
-        <v>1E-3</v>
+      <c r="F16" s="27">
+        <v>5.976</v>
+      </c>
+      <c r="G16" s="28">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H16" s="29">
-        <v>5.976</v>
-      </c>
-      <c r="I16" s="30">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J16" s="31">
         <v>1.2310000000000001</v>
       </c>
-      <c r="K16" s="31">
+      <c r="I16" s="29">
         <v>2E-3</v>
       </c>
+      <c r="J16" s="20">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="K16" s="15">
+        <v>6.0000000000000001E-3</v>
+      </c>
       <c r="L16" s="22">
-        <v>0.57299999999999995</v>
-      </c>
-      <c r="M16" s="16">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="N16" s="24">
         <v>1.2490000000000001</v>
       </c>
-      <c r="O16" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="P16" s="33">
+      <c r="M16" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="N16" s="31">
         <v>18.606000000000002</v>
       </c>
-      <c r="Q16" s="32">
+      <c r="O16" s="30">
         <v>0.249</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75">
+    <row r="17" spans="1:15" ht="15.75">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1906,50 +1815,44 @@
       <c r="C17" s="4">
         <v>1.2E-2</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="19">
         <v>6.0650000000000004</v>
       </c>
       <c r="E17" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F17" s="21">
-        <v>1.617</v>
-      </c>
-      <c r="G17" s="12">
-        <v>2E-3</v>
+      <c r="F17" s="27">
+        <v>8.7669999999999995</v>
+      </c>
+      <c r="G17" s="28">
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H17" s="29">
-        <v>8.7669999999999995</v>
-      </c>
-      <c r="I17" s="30">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="J17" s="31">
         <v>1.365</v>
       </c>
-      <c r="K17" s="31">
+      <c r="I17" s="29">
         <v>3.0000000000000001E-3</v>
       </c>
+      <c r="J17" s="20">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="K17" s="15">
+        <v>1E-3</v>
+      </c>
       <c r="L17" s="22">
-        <v>0.88400000000000001</v>
-      </c>
-      <c r="M17" s="16">
-        <v>1E-3</v>
-      </c>
-      <c r="N17" s="24">
         <v>1.7390000000000001</v>
       </c>
-      <c r="O17" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="P17" s="33">
+      <c r="M17" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="N17" s="31">
         <v>28.033999999999999</v>
       </c>
-      <c r="Q17" s="32">
+      <c r="O17" s="30">
         <v>0.70499999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75">
+    <row r="18" spans="1:15" ht="15.75">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1959,150 +1862,133 @@
       <c r="C18" s="4">
         <v>1E-3</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="19">
         <v>13.436999999999999</v>
       </c>
       <c r="E18" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F18" s="21">
-        <v>3.9889999999999999</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.106</v>
+      <c r="F18" s="27">
+        <v>20.856999999999999</v>
+      </c>
+      <c r="G18" s="28">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H18" s="29">
-        <v>20.856999999999999</v>
-      </c>
-      <c r="I18" s="30">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J18" s="31">
         <v>1.7549999999999999</v>
       </c>
-      <c r="K18" s="31">
+      <c r="I18" s="29">
         <v>5.0000000000000001E-3</v>
       </c>
+      <c r="J18" s="20">
+        <v>1.9359999999999999</v>
+      </c>
+      <c r="K18" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
       <c r="L18" s="22">
-        <v>1.9359999999999999</v>
-      </c>
-      <c r="M18" s="16">
+        <v>3.988</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="N18" s="31">
+        <v>54.719000000000001</v>
+      </c>
+      <c r="O18" s="30">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16.5" thickBot="1">
+      <c r="A19" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="21">
+        <v>243.57</v>
+      </c>
+      <c r="C19" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="D19" s="21">
+        <v>17.957999999999998</v>
+      </c>
+      <c r="E19" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="F19" s="27">
+        <v>27.492999999999999</v>
+      </c>
+      <c r="G19" s="28">
+        <v>1.2E-2</v>
+      </c>
+      <c r="H19" s="29">
+        <v>2.0259999999999998</v>
+      </c>
+      <c r="I19" s="29">
+        <v>0.01</v>
+      </c>
+      <c r="J19" s="21">
+        <v>2.649</v>
+      </c>
+      <c r="K19" s="21">
+        <v>2E-3</v>
+      </c>
+      <c r="L19" s="21">
+        <v>5.2519999999999998</v>
+      </c>
+      <c r="M19" s="21">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="N18" s="24">
-        <v>3.988</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="P18" s="33">
-        <v>54.719000000000001</v>
-      </c>
-      <c r="Q18" s="32">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="16.5" thickBot="1">
-      <c r="A19" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="23">
-        <v>243.57</v>
-      </c>
-      <c r="C19" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="D19" s="23">
-        <v>17.957999999999998</v>
-      </c>
-      <c r="E19" s="23">
-        <v>2E-3</v>
-      </c>
-      <c r="F19" s="23">
-        <v>5.056</v>
-      </c>
-      <c r="G19" s="23">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="H19" s="29">
-        <v>27.492999999999999</v>
-      </c>
-      <c r="I19" s="30">
-        <v>1.2E-2</v>
-      </c>
-      <c r="J19" s="31">
-        <v>2.0259999999999998</v>
-      </c>
-      <c r="K19" s="31">
-        <v>0.01</v>
-      </c>
-      <c r="L19" s="23">
-        <v>2.649</v>
-      </c>
-      <c r="M19" s="23">
-        <v>2E-3</v>
-      </c>
-      <c r="N19" s="23">
-        <v>5.2519999999999998</v>
-      </c>
-      <c r="O19" s="23">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="P19" s="33">
+      <c r="N19" s="31">
         <v>81.644000000000005</v>
       </c>
-      <c r="Q19" s="32">
+      <c r="O19" s="30">
         <v>0.38700000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="16.5" thickBot="1">
-      <c r="A20" s="34" t="s">
+    <row r="20" spans="1:15" ht="16.5" thickBot="1">
+      <c r="A20" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="33">
         <f>SUM(B5:B19)</f>
         <v>634.9079999999999</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35">
+      <c r="C20" s="33"/>
+      <c r="D20" s="33">
         <f>SUM(D5:D19)</f>
         <v>47.997</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35">
+      <c r="E20" s="33"/>
+      <c r="F20" s="33">
         <f>SUM(F5:F19)</f>
-        <v>22.989000000000001</v>
-      </c>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35">
-        <f>SUM(H5:H19)</f>
         <v>77.009999999999991</v>
       </c>
-      <c r="I20" s="35"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33">
+        <v>18.209999999999997</v>
+      </c>
+      <c r="I20" s="33"/>
       <c r="J20" s="35">
-        <v>18.209999999999997</v>
-      </c>
-      <c r="K20" s="35"/>
-      <c r="L20" s="37">
+        <f>SUM(J5:J19)</f>
+        <v>6.9869999999999992</v>
+      </c>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33">
         <f>SUM(L5:L19)</f>
-        <v>6.9869999999999992</v>
-      </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35">
-        <f>SUM(N5:N19)</f>
         <v>14.183</v>
       </c>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35">
+      <c r="M20" s="33"/>
+      <c r="N20" s="33">
         <v>249.285</v>
       </c>
-      <c r="Q20" s="35"/>
-    </row>
-    <row r="21" spans="1:17" s="6" customFormat="1" ht="15.75">
-      <c r="A21" s="13"/>
+      <c r="O20" s="33"/>
+    </row>
+    <row r="21" spans="1:15" s="6" customFormat="1" ht="15.75">
+      <c r="A21" s="12"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="14"/>
+      <c r="D21" s="13"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -2112,10 +1998,8 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-    </row>
-    <row r="22" spans="1:17" ht="15.75">
+    </row>
+    <row r="22" spans="1:15" ht="15.75">
       <c r="A22" s="8" t="s">
         <v>1</v>
       </c>
@@ -2124,146 +2008,128 @@
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A23" s="39" t="s">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A23" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+    </row>
+    <row r="24" spans="1:15" s="6" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A24" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75">
+      <c r="A25" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+    </row>
+    <row r="26" spans="1:15" s="24" customFormat="1" ht="15.75">
+      <c r="A26" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-    </row>
-    <row r="24" spans="1:17" s="6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A24" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-    </row>
-    <row r="25" spans="1:17" ht="15.75">
-      <c r="A25" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="40"/>
-    </row>
-    <row r="26" spans="1:17" s="26" customFormat="1" ht="15.75">
-      <c r="A26" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75">
-      <c r="A27" s="27" t="s">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75">
+      <c r="A27" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75">
+      <c r="A28" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75">
-      <c r="A28" s="27" t="s">
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="28" t="s">
+      <c r="B29" s="26"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30" s="25" t="s">
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="24"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-    </row>
-    <row r="32" spans="1:17" ht="15.75">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75">
       <c r="A32" s="10"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2292,20 +2158,19 @@
       <c r="E35" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A24:Q24"/>
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="H3:Q3"/>
+  <mergeCells count="14">
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="F3:O3"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
   </mergeCells>
